--- a/Server/Received_data/Model/Output_3.xlsx
+++ b/Server/Received_data/Model/Output_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,300 +442,300 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_1')</t>
+          <t>('Asm_280', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_3', 'Component_4')</t>
+          <t>('C_org', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_1')</t>
+          <t>('E2E3', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
+          <t>('C_org', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_4')</t>
+          <t>('E2E3', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_3')</t>
+          <t>('FIX', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_3')</t>
+          <t>('E2E3', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'FIX')</t>
+          <t>('C_org', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_1')</t>
+          <t>('Asm_350', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_3')</t>
+          <t>('Asm_350', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Asm_280')</t>
+          <t>('Asm_280', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'FIX')</t>
+          <t>('Asm_280', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_4')</t>
+          <t>('Asm_280', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1', 'Component_3')</t>
+          <t>('Asm_350', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1', 'Component_2')</t>
+          <t>('Asm_350', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'FIX')</t>
+          <t>('Asm_280', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_3')</t>
+          <t>('C_org', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_2', 'Component_3')</t>
+          <t>('Asm_350', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_4')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
+          <t>('C_org', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'FIX')</t>
+          <t>('E2E3', 'C_org', 'HIX')</t>
         </is>
       </c>
     </row>
@@ -744,1216 +744,1216 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_4')</t>
+          <t>('E2E3', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1', 'Component_4')</t>
+          <t>('Suva', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_2')</t>
+          <t>('Suva', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'Component_3')</t>
+          <t>('Asm_280', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_2', 'Component_4')</t>
+          <t>('E2E3', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_1')</t>
+          <t>('C_org', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'FIX')</t>
+          <t>('C_org', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_1')</t>
+          <t>('C_org', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Asm_280')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'FIX')</t>
+          <t>('FIX', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B35" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'HIX')</t>
+          <t>('Asm_350', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="B36" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_2', 'Component_3')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B37" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_3', 'Component_4')</t>
+          <t>('FIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B38" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'HIX')</t>
+          <t>('C_org', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="B39" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_2', 'Component_4')</t>
+          <t>('Suva', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="B40" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'HIX')</t>
+          <t>('Suva', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="B41" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_2', 'Component_4')</t>
+          <t>('C_org', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="B42" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>('Component_2', 'Component_3', 'Component_4')</t>
+          <t>('E2E3', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_2')</t>
+          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_4')</t>
+          <t>('E2E3', 'C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1', 'Component_4')</t>
+          <t>('E2E3', 'C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B46" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1', 'Component_3')</t>
+          <t>('Asm_350', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="B47" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_3')</t>
+          <t>('Asm_280', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B48" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_1')</t>
+          <t>('Asm_350', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="B49" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'Component_3')</t>
+          <t>('E2E3', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="B50" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_4')</t>
+          <t>('E2E3', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'HIX')</t>
+          <t>('E2E3', 'C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B52" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_1')</t>
+          <t>('E2E3', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="B53" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1', 'Component_3')</t>
+          <t>('E2E3', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="B54" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_1')</t>
+          <t>('C_org', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="B55" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1', 'Component_2')</t>
+          <t>('C_org', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="B56" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_3')</t>
+          <t>('E2E3', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="B57" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_2')</t>
+          <t>('C_org', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_2', 'Component_4')</t>
+          <t>('Asm_350', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B59" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_1')</t>
+          <t>('Asm_350', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="B60" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_3')</t>
+          <t>('Suva', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="B61" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_2')</t>
+          <t>('C_org', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="B62" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_2', 'Component_3')</t>
+          <t>('Suva', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="B63" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'HIX')</t>
+          <t>('C_org', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="B64" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
+          <t>('C_org', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B65" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_4')</t>
+          <t>('C_org', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'HIX')</t>
+          <t>('Suva', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Asm_280')</t>
+          <t>('Suva', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="B68" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Asm_280')</t>
+          <t>('Suva', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B69" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Component_3')</t>
+          <t>('C_org', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B70" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_2')</t>
+          <t>('Asm_350', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="B71" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1', 'Component_4')</t>
+          <t>('Asm_350', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="B72" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1', 'Component_2')</t>
+          <t>('HIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_3', 'Component_4')</t>
+          <t>('Suva', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="B74" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_4')</t>
+          <t>('C_org', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_4')</t>
+          <t>('C_org', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="B76" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_2')</t>
+          <t>('C_org', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1', 'Component_4')</t>
+          <t>('Suva', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="B78" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_2', 'Component_4')</t>
+          <t>('E2E3', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="B79" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_1')</t>
+          <t>('E2E3', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B80" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_4')</t>
+          <t>('C_org', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B81" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'FIX')</t>
+          <t>('E2E3', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'HIX')</t>
+          <t>('E2E3', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="B85" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B86" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'HIX')</t>
+          <t>('Asm_280', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B87" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'Component_1')</t>
+          <t>('C_org', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B88" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'FIX')</t>
+          <t>('E2E3', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B89" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_1', 'Component_3')</t>
+          <t>('C_org', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B90" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_2', 'Component_3')</t>
+          <t>('FIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B91" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'Component_1')</t>
+          <t>('Asm_280', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B92" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Component_3')</t>
+          <t>('C_org', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_2', 'Component_3')</t>
+          <t>('Asm_280', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="B94" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'HIX')</t>
+          <t>('HIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="B95" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1', 'Component_2')</t>
+          <t>('Suva', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B96" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_3', 'Component_4')</t>
+          <t>('Suva', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="B97" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Component_3')</t>
+          <t>('FIX', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B98" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_2')</t>
+          <t>('Component_1', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="B99" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Component_1')</t>
+          <t>('E2E3', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'FIX')</t>
+          <t>('E2E3', 'C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B101" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'FIX')</t>
+          <t>('E2E3', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B102" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Component_3')</t>
+          <t>('C_org', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B103" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_3', 'Component_4')</t>
+          <t>('Suva', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B104" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_2')</t>
+          <t>('Suva', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B105" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Asm_280')</t>
+          <t>('Suva', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B106" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX', 'Component_2')</t>
+          <t>('HIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B107" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_3', 'Component_4')</t>
+          <t>('E2E3', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B108" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX', 'Component_4')</t>
+          <t>('Suva', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B109" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'HIX')</t>
+          <t>('Suva', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B110" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_2', 'Component_4')</t>
+          <t>('C_org', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B111" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_2')</t>
+          <t>('E2E3', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B112" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_1', 'Component_2')</t>
+          <t>('C_org', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="B113" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'HIX')</t>
+          <t>('E2E3', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B114" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_4')</t>
+          <t>('Suva', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B115" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_2', 'Component_4')</t>
+          <t>('Suva', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="B116" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_2')</t>
+          <t>('E2E3', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B117" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX', 'Component_3')</t>
+          <t>('E2E3', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B118" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -1963,625 +1963,40 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="B119" t="n">
-        <v>0.696969696969697</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'HIX')</t>
+          <t>('FIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B120" t="n">
-        <v>0.696969696969697</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'Component_4')</t>
+          <t>('E2E3', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B121" t="n">
-        <v>0.696969696969697</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'HIX')</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B122" t="n">
-        <v>0.696969696969697</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B123" t="n">
-        <v>0.696969696969697</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_2', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B124" t="n">
-        <v>0.696969696969697</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_1', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B125" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B126" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_1', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B127" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B128" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_3', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>163</v>
-      </c>
-      <c r="B129" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_3', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B130" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_1', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B131" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B132" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B133" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B134" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B135" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_2', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B136" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B137" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_1', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B138" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>161</v>
-      </c>
-      <c r="B139" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_2', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B140" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B141" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_1', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B142" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B143" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Asm_350')</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B144" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_2', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B145" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B146" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'HIX')</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B147" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B148" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B149" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Asm_350')</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B150" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_3')</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'HIX')</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
           <t>('E2E3', 'Asm_350', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B158" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Asm_350')</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Suva')</t>
         </is>
       </c>
     </row>

--- a/Server/Received_data/Model/Output_3.xlsx
+++ b/Server/Received_data/Model/Output_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,228 +436,284 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Feature</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'FIX', 'Component_2')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8529411764705882</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>('C_org', 'HIX', 'Component_2')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280', 'HIX')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280', 'FIX')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX', 'Component_3')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>('FIX', 'HIX', 'Component_1')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX', 'Component_1')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX', 'HIX')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'HIX')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280', 'HIX')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'HIX', 'Component_1')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'HIX', 'Component_3')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'HIX', 'Component_1')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'FIX', 'HIX')</t>
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'HIX', 'Component_3')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'FIX', 'Component_3')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'FIX', 'Component_1')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
@@ -666,9 +722,12 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C19" t="inlineStr">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>('E2E3', 'Asm_350', 'HIX')</t>
         </is>
@@ -676,742 +735,913 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280', 'Component_2')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'FIX', 'HIX')</t>
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'FIX')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'HIX')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'HIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280', 'FIX')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'FIX', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('E2E3', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280', 'FIX')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('E2E3', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_2')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('E2E3', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280', 'HIX')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('E2E3', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'HIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('E2E3', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('E2E3', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>('FIX', 'HIX', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('E2E3', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'FIX', 'Component_1')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_2', 'Component_3')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>('C_org', 'FIX', 'Component_2')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Asm_280')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280', 'HIX')</t>
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_2', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280', 'Component_1')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Asm_280')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_1', 'Component_2')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'HIX', 'Component_2')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280', 'FIX')</t>
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'HIX')</t>
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'FIX')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280', 'Component_2')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>('C_org', 'FIX', 'HIX')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Component_2')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'FIX')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>('C_org', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Asm_280')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>('C_org', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'HIX', 'Component_2')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>('C_org', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_2', 'Component_3')</t>
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>('C_org', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'FIX')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>('C_org', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'FIX')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>('C_org', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX', 'Component_2')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>('C_org', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>('C_org', 'HIX', 'Component_3')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>('C_org', 'FIX', 'Component_3')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_1', 'Component_2')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX', 'Component_1')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>('C_org', 'HIX', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_1', 'Component_3')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'FIX', 'Component_2')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_1', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX', 'Component_3')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>('C_org', 'FIX', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
@@ -1420,9 +1650,12 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C77" t="inlineStr">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>('Suva', 'FIX', 'HIX')</t>
         </is>
@@ -1430,573 +1663,705 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Component_1')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>('Suva', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Asm_280')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>('Suva', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Asm_280')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>('Suva', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_3')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>('Suva', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Component_3')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>('Suva', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>('Suva', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Asm_350')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Component_1')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_1', 'Component_3')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva', 'Asm_350')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_1', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_1', 'Component_3')</t>
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_2', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_1', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_1', 'Component_2')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_2', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_1')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>('FIX', 'HIX', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_2', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX', 'Component_1')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org', 'Suva')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350', 'Component_1')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280', 'Component_1')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_2', 'Component_3')</t>
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280', 'Component_3')</t>
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_1', 'Component_2')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_2', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>('FIX', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'FIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>('FIX', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>('FIX', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva', 'Asm_350')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_1', 'Component_2')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX', 'Component_2')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_1', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.3823529411764706</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350', 'Component_2')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>('Component_1', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>

--- a/Server/Received_data/Model/Output_3.xlsx
+++ b/Server/Received_data/Model/Output_3.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>LDA_macro</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -447,465 +447,465 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8261904761904761</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Suva')</t>
+          <t>('C_org', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8047619047619047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Asm_350')</t>
+          <t>('C_org', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.7824675324675325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Asm_280')</t>
+          <t>('C_org', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.7459415584415584</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'FIX')</t>
+          <t>('C_org', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.7227443609022556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'HIX')</t>
+          <t>('C_org', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Component_1')</t>
+          <t>('E2E3', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6215538847117795</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Component_2')</t>
+          <t>('E2E3', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6211484593837534</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org', 'Component_3')</t>
+          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6139971139971141</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Asm_350')</t>
+          <t>('E2E3', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.6119047619047618</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Asm_280')</t>
+          <t>('C_org', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5962566844919787</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'FIX')</t>
+          <t>('E2E3', 'C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.5863095238095238</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'HIX')</t>
+          <t>('E2E3', 'Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5803571428571429</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Component_1')</t>
+          <t>('E2E3', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5803571428571429</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Component_2')</t>
+          <t>('E2E3', 'C_org', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva', 'Component_3')</t>
+          <t>('C_org', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Asm_280')</t>
+          <t>('E2E3', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'FIX')</t>
+          <t>('Asm_280', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5702838827838829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'HIX')</t>
+          <t>('E2E3', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5680272108843537</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Component_1')</t>
+          <t>('E2E3', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5663780663780664</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Component_2')</t>
+          <t>('C_org', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.5662878787878788</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350', 'Component_3')</t>
+          <t>('C_org', 'Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.5659983291562238</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'FIX')</t>
+          <t>('E2E3', 'C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'HIX')</t>
+          <t>('E2E3', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5545787545787546</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_1')</t>
+          <t>('E2E3', 'Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_2')</t>
+          <t>('C_org', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5259103641456583</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.5255102040816327</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'HIX')</t>
+          <t>('Asm_280', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.5255102040816327</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'Component_1')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5204081632653061</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX', 'Component_2')</t>
+          <t>('E2E3', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
@@ -914,10 +914,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.5187590187590188</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -927,657 +927,657 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5144110275689223</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX', 'Component_1')</t>
+          <t>('Asm_280', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.5120300751879699</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX', 'Component_2')</t>
+          <t>('E2E3', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.5120300751879699</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX', 'Component_3')</t>
+          <t>('FIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.5095238095238095</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_1', 'Component_2')</t>
+          <t>('E2E3', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.5095238095238095</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_1', 'Component_3')</t>
+          <t>('E2E3', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.5089285714285714</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_2', 'Component_3')</t>
+          <t>('FIX', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="B38" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5089285714285714</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Asm_350')</t>
+          <t>('Asm_280', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.5089285714285714</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Asm_280')</t>
+          <t>('C_org', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B40" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.5010185892538833</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'FIX')</t>
+          <t>('FIX', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4880413703943116</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'HIX')</t>
+          <t>('C_org', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4846491228070176</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Component_1')</t>
+          <t>('E2E3', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Component_2')</t>
+          <t>('E2E3', 'Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B44" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva', 'Component_3')</t>
+          <t>('Suva', 'Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Asm_280')</t>
+          <t>('Suva', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="B46" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'FIX')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="B47" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'HIX')</t>
+          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Component_1')</t>
+          <t>('C_org', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B49" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4653679653679653</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Component_2')</t>
+          <t>('Asm_350', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="B50" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.4653679653679653</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350', 'Component_3')</t>
+          <t>('FIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4533995416348358</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'FIX')</t>
+          <t>('FIX', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B52" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'HIX')</t>
+          <t>('C_org', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.45</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_1')</t>
+          <t>('C_org', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4484126984126984</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_2')</t>
+          <t>('C_org', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B55" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.444996180290298</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280', 'Component_3')</t>
+          <t>('E2E3', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B56" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.444996180290298</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'HIX')</t>
+          <t>('E2E3', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.4438775510204082</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_1')</t>
+          <t>('Suva', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B58" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.440422322775264</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_2')</t>
+          <t>('Suva', 'Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B59" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.440422322775264</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX', 'Component_3')</t>
+          <t>('Suva', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B60" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4393939393939394</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_1')</t>
+          <t>('C_org', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B61" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4393939393939394</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_2')</t>
+          <t>('C_org', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX', 'Component_3')</t>
+          <t>('C_org', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B63" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_1', 'Component_2')</t>
+          <t>('E2E3', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="B64" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_1', 'Component_3')</t>
+          <t>('Asm_280', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="B65" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_2', 'Component_3')</t>
+          <t>('Asm_280', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.4337068160597572</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Asm_280')</t>
+          <t>('C_org', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'FIX')</t>
+          <t>('C_org', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B68" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4325396825396825</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'HIX')</t>
+          <t>('Suva', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.430672268907563</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Component_1')</t>
+          <t>('Asm_350', 'Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B70" t="n">
-        <v>0.696969696969697</v>
+        <v>0.42742673992674</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Component_2')</t>
+          <t>('Asm_350', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B71" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.42742673992674</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350', 'Component_3')</t>
+          <t>('Asm_350', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="B72" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.425</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'FIX')</t>
+          <t>('E2E3', 'C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
@@ -1586,10 +1586,10 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4246031746031746</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1599,769 +1599,769 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B74" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4246031746031746</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_1')</t>
+          <t>('Asm_280', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B75" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4246031746031746</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_2')</t>
+          <t>('Asm_280', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B76" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4222689075630252</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280', 'Component_3')</t>
+          <t>('C_org', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="B77" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4217687074829932</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'HIX')</t>
+          <t>('HIX', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B78" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.4184981684981685</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'Component_1')</t>
+          <t>('C_org', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B79" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.4170068027210885</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'Component_2')</t>
+          <t>('Suva', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B80" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.4167919799498747</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX', 'Component_3')</t>
+          <t>('E2E3', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B81" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.4121956474897652</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX', 'Component_1')</t>
+          <t>('Suva', 'HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.4103641456582633</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX', 'Component_2')</t>
+          <t>('Suva', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.4098639455782313</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX', 'Component_3')</t>
+          <t>('Suva', 'HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B84" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4095238095238095</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_1', 'Component_2')</t>
+          <t>('C_org', 'Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="B85" t="n">
-        <v>0.696969696969697</v>
+        <v>0.4068627450980392</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_1', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="B86" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.3831501831501832</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_2', 'Component_3')</t>
+          <t>('E2E3', 'Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="B87" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.3830532212885154</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'FIX')</t>
+          <t>('C_org', 'Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="B88" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.376984126984127</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'HIX')</t>
+          <t>('HIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="B89" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.376984126984127</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_1')</t>
+          <t>('HIX', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>0.376984126984127</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_2')</t>
+          <t>('Asm_280', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B91" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.376984126984127</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280', 'Component_3')</t>
+          <t>('Asm_280', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B92" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3708791208791209</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'HIX')</t>
+          <t>('Asm_350', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B93" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.3664596273291925</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_1')</t>
+          <t>('E2E3', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B94" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3664596273291925</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_2')</t>
+          <t>('Component_1', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="B95" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.3611626468769326</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B96" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3611626468769326</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_1')</t>
+          <t>('E2E3', 'C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B97" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_2')</t>
+          <t>('Suva', 'HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3520923520923521</v>
       </c>
       <c r="C98" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX', 'Component_3')</t>
+          <t>('Asm_350', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B99" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3520923520923521</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1', 'Component_2')</t>
+          <t>('FIX', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3520923520923521</v>
       </c>
       <c r="C100" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1', 'Component_3')</t>
+          <t>('Asm_350', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="B101" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.3520408163265306</v>
       </c>
       <c r="C101" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_2', 'Component_3')</t>
+          <t>('C_org', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B102" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.3446115288220551</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'HIX')</t>
+          <t>('E2E3', 'Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B103" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.3391053391053392</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_1')</t>
+          <t>('Asm_350', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>0.3363095238095238</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_2')</t>
+          <t>('C_org', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="B105" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.3324675324675325</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX', 'Component_3')</t>
+          <t>('C_org', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="B106" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.3311688311688312</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_1')</t>
+          <t>('Suva', 'FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="B107" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3306878306878307</v>
       </c>
       <c r="C107" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_2')</t>
+          <t>('E2E3', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="B108" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3290598290598291</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX', 'Component_3')</t>
+          <t>('E2E3', 'Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B109" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="C109" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1', 'Component_2')</t>
+          <t>('Suva', 'Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B110" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1', 'Component_3')</t>
+          <t>('Suva', 'Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="B111" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3197278911564626</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_2', 'Component_3')</t>
+          <t>('E2E3', 'C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="B112" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.3102453102453103</v>
       </c>
       <c r="C112" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_1')</t>
+          <t>('Suva', 'Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B113" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.2977443609022557</v>
       </c>
       <c r="C113" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_2')</t>
+          <t>('Asm_350', 'FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.2817460317460317</v>
       </c>
       <c r="C114" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX', 'Component_3')</t>
+          <t>('Asm_350', 'Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B115" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="C115" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1', 'Component_2')</t>
+          <t>('Suva', 'Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="B116" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.269047619047619</v>
       </c>
       <c r="C116" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1', 'Component_3')</t>
+          <t>('Suva', 'Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B117" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.2676767676767677</v>
       </c>
       <c r="C117" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_2', 'Component_3')</t>
+          <t>('Asm_350', 'FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="B118" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.2658730158730159</v>
       </c>
       <c r="C118" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1', 'Component_2')</t>
+          <t>('Suva', 'Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="B119" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.2622465254044201</v>
       </c>
       <c r="C119" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1', 'Component_3')</t>
+          <t>('Asm_350', 'FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B120" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.2510204081632653</v>
       </c>
       <c r="C120" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_2', 'Component_3')</t>
+          <t>('Suva', 'Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="B121" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.2342219184324447</v>
       </c>
       <c r="C121" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_2', 'Component_3')</t>
+          <t>('Suva', 'Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
